--- a/docs/oc-regiones/gas-licuado-de-petroleo/tarapaca.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M194"/>
+  <dimension ref="A1:M196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>474.82</v>
+        <v>470.8</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>174.04</v>
+        <v>173.15</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2140.23</v>
+        <v>2118.87</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>54.09</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1472.72</v>
+        <v>1458.02</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>235.77</v>
+        <v>233.42</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>196.36</v>
+        <v>194.31</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>196.36</v>
+        <v>194.31</v>
       </c>
     </row>
     <row r="10">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1030.9</v>
+        <v>1025.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2013-2112-CM25</t>
+          <t>1079967-637-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>191.28</v>
+        <v>122.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1079967-637-CM25</t>
+          <t>2013-2112-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>124.33</v>
+        <v>189.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1227-212-CM25</t>
+          <t>3349-380-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>696.11</v>
+        <v>713.35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1227-211-CM25</t>
+          <t>1407-15753-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>239.09</v>
+        <v>285.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3349-380-CM25</t>
+          <t>1227-211-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>717.28</v>
+        <v>237.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1407-15753-CM25</t>
+          <t>1227-212-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>286.91</v>
+        <v>692.3</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>956.38</v>
+        <v>959.79</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>584.51</v>
+        <v>590.87</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>765.1</v>
+        <v>778.3099999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>119.55</v>
+        <v>121.61</v>
       </c>
     </row>
     <row r="21">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2562.38</v>
+        <v>2574.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3159-162-CM25</t>
+          <t>1346281-188-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,17 +1754,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>108.23</v>
+        <v>1076.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1346281-188-CM25</t>
+          <t>3159-162-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1069.11</v>
+        <v>109.01</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>383.57</v>
+        <v>382.89</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>65.88</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>988.17</v>
+        <v>984.1</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>235.28</v>
+        <v>234.91</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1189.54</v>
+        <v>1187.7</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1024.93</v>
+        <v>1030.23</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>446.56</v>
+        <v>440.79</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>595.41</v>
+        <v>587.85</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>292.25</v>
+        <v>288.54</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>876.75</v>
+        <v>865.62</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>893.12</v>
+        <v>881.78</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>195.35</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="36">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>143.01</v>
+        <v>142.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3349-416-CM25</t>
+          <t>1407-15855-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>56.11</v>
+        <v>428.77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1407-15855-CM25</t>
+          <t>3349-416-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>433.79</v>
+        <v>55.46</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>992.88</v>
+        <v>996.6900000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>756.48</v>
+        <v>759.9</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>94.56</v>
+        <v>94.98999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>141.84</v>
+        <v>142.22</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>118.2</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1659.91</v>
+        <v>1671.34</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>573.59</v>
+        <v>578.49</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>430.19</v>
+        <v>433.87</v>
       </c>
     </row>
     <row r="47">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>567.36</v>
+        <v>574.33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1070620-248-CM26</t>
+          <t>3239-2-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.942.200-7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>ESTACION AERONAVAL IQUIQUE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1048.83</v>
+        <v>246.55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3239-2-CM26</t>
+          <t>1070620-248-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.942.200-7</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ESTACION AERONAVAL IQUIQUE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>249.72</v>
+        <v>1035.52</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>993.5</v>
+        <v>979.1799999999999</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>607.41</v>
+        <v>608.25</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>248.38</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>149.03</v>
+        <v>149.23</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>195.47</v>
+        <v>194.44</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>244.34</v>
+        <v>243.05</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>781.88</v>
+        <v>787</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1197.25</v>
+        <v>1215.48</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>488.67</v>
+        <v>500.56</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1026.21</v>
+        <v>1051.17</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>107.51</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>143.77</v>
+        <v>148.05</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8155.83</v>
+        <v>8398.25</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>601.34</v>
+        <v>599.2</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>476.06</v>
+        <v>474.36</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>147.44</v>
+        <v>146.33</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>982.9</v>
+        <v>975.54</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1098.08</v>
+        <v>1089.86</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1523.5</v>
+        <v>1512.09</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2703.53</v>
+        <v>2711.36</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1537.31</v>
+        <v>1545.25</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>400.09</v>
+        <v>401.19</v>
       </c>
     </row>
     <row r="72">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>121.14</v>
+        <v>122.24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3145-32-CM26</t>
+          <t>3145-29-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>343.39</v>
+        <v>243.87</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3145-29-CM26</t>
+          <t>3145-32-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>242.27</v>
+        <v>345.65</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1005.95</v>
+        <v>1014.91</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3391.84</v>
+        <v>3386.02</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2076.93</v>
+        <v>2074.79</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>144.36</v>
+        <v>143.33</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>589.74</v>
+        <v>586.53</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>130.3</v>
+        <v>129.53</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1385.87</v>
+        <v>1377.45</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1652.03</v>
+        <v>1645.65</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>227.4</v>
+        <v>226.53</v>
       </c>
     </row>
     <row r="84">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>963.5700000000001</v>
+        <v>968.5599999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3447-522-CM26</t>
+          <t>2013-238-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5597,17 +5597,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1912.86</v>
+        <v>188.42</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2013-238-CM26</t>
+          <t>3447-522-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5658,17 +5658,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>183.1</v>
+        <v>1968.42</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2591-140-CM26</t>
+          <t>722640-31-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5719,17 +5719,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>69.250.400-3</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>I MUNICIPALIDAD DE COLCHANE</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>378.75</v>
+        <v>232.65</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>722640-31-CM26</t>
+          <t>2591-140-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5780,17 +5780,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.250.400-3</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLCHANE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>228.87</v>
+        <v>384.99</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>996.97</v>
+        <v>999.42</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>459.71</v>
+        <v>460.84</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>343.37</v>
+        <v>338.95</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>759.6</v>
+        <v>771.5</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>237.37</v>
+        <v>241.09</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>143.59</v>
+        <v>145.84</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>593.24</v>
+        <v>593.21</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>145.56</v>
+        <v>144.91</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>194.08</v>
+        <v>193.22</v>
       </c>
     </row>
     <row r="98">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>482.6</v>
+        <v>479.82</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>794947-26-CM26</t>
+          <t>1070620-2944-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>217.17</v>
+        <v>1006.96</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2591-211-CM26</t>
+          <t>794947-26-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>236.46</v>
+        <v>215.78</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1070620-2944-CM26</t>
+          <t>2591-211-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1013.45</v>
+        <v>234.95</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1411.59</v>
+        <v>1405.51</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>241.3</v>
+        <v>240.26</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1935.61</v>
+        <v>1907.61</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>731.58</v>
+        <v>718.3200000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>579.17</v>
+        <v>568.67</v>
       </c>
     </row>
     <row r="107">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8088.46</v>
+        <v>7871.88</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3208-73-CM26</t>
+          <t>3208-72-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>180.11</v>
+        <v>180.64</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3208-72-CM26</t>
+          <t>3208-73-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>180.11</v>
+        <v>180.64</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>180.11</v>
+        <v>181.64</v>
       </c>
     </row>
     <row r="111">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>641.13</v>
+        <v>646.5700000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1350296-674-CM26</t>
+          <t>1079967-175-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4030.08</v>
+        <v>236.04</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1079967-175-CM26</t>
+          <t>1350296-674-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>236.44</v>
+        <v>4023.34</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>480.3</v>
+        <v>486.21</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>918.62</v>
+        <v>929.92</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>945.76</v>
+        <v>958.1</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>710.91</v>
+        <v>728.41</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>433.16</v>
+        <v>434.52</v>
       </c>
     </row>
     <row r="119">
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1205.13</v>
+        <v>1210.12</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3208-95-CM26</t>
+          <t>1794-14-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>172.16</v>
+        <v>313.89</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1794-14-CM26</t>
+          <t>3208-95-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>315.24</v>
+        <v>171.42</v>
       </c>
     </row>
     <row r="122">
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>143.51</v>
+        <v>142.65</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3145-246-CM26</t>
+          <t>1227-117-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7915,17 +7915,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>292.98</v>
+        <v>882.24</v>
       </c>
     </row>
     <row r="124">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>292.98</v>
+        <v>289</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1227-117-CM26</t>
+          <t>3145-246-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8037,17 +8037,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>894.4</v>
+        <v>289</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>937.54</v>
+        <v>929.54</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1464.9</v>
+        <v>1481.28</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1916.96</v>
+        <v>1938.4</v>
       </c>
     </row>
     <row r="129">
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>584.63</v>
+        <v>591.17</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1407-265-CM26</t>
+          <t>3159-62-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8342,17 +8342,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>779.51</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3159-62-CM26</t>
+          <t>1407-265-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8403,17 +8403,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>128.91</v>
+        <v>785.42</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2683.75</v>
+        <v>2676.97</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1671.59</v>
+        <v>1687.47</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2900.06</v>
+        <v>2921.66</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>623.08</v>
+        <v>627.72</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1727.52</v>
+        <v>1723.26</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>189.71</v>
+        <v>190.64</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4776.77</v>
+        <v>4800.23</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>771.5599999999999</v>
+        <v>775.35</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3585.76</v>
+        <v>3597.17</v>
       </c>
     </row>
     <row r="141">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>269.79</v>
+        <v>270.65</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3352-94-CM26</t>
+          <t>3349-179-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>962.23</v>
+        <v>19885.08</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3349-179-CM26</t>
+          <t>3352-94-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>19779.91</v>
+        <v>967.35</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1347772-40-CM26</t>
+          <t>3145-320-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1281.79</v>
+        <v>630.38</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3145-324-CM26</t>
+          <t>3145-322-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>996.91</v>
+        <v>315.19</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3145-322-CM26</t>
+          <t>3145-324-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>311.53</v>
+        <v>1008.6</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3145-320-CM26</t>
+          <t>1347772-40-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>623.0700000000001</v>
+        <v>1296.82</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1171177-21-CM26</t>
+          <t>838102-63-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>519.27</v>
+        <v>890.97</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>838102-63-CM26</t>
+          <t>1171177-21-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>Centro de Educación y Trabajo</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>906.28</v>
+        <v>510.49</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1416.06</v>
+        <v>1395.97</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>413.27</v>
+        <v>407.6</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>283.21</v>
+        <v>279.32</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1132.85</v>
+        <v>1117.29</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1812.56</v>
+        <v>1787.66</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>552.83</v>
+        <v>545.24</v>
       </c>
     </row>
     <row r="156">
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>705</v>
+        <v>708.2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3208-132-CM26</t>
+          <t>1227-158-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9989,17 +9989,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>173.09</v>
+        <v>6653.79</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1227-158-CM26</t>
+          <t>3208-132-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10050,17 +10050,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>6529.65</v>
+        <v>176.38</v>
       </c>
     </row>
     <row r="159">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2969.63</v>
+        <v>2990.14</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3145-384-CM26</t>
+          <t>3145-385-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>873.88</v>
+        <v>899.6799999999999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3145-385-CM26</t>
+          <t>3145-384-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>902.0700000000001</v>
+        <v>871.5599999999999</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>141.3</v>
+        <v>139.42</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1197.79</v>
+        <v>1173.18</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>570.38</v>
+        <v>558.66</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>285.19</v>
+        <v>279.33</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>258.95</v>
+        <v>253.63</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1127.4</v>
+        <v>1138.11</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>276.74</v>
+        <v>279.37</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>676.4400000000001</v>
+        <v>682.87</v>
       </c>
     </row>
     <row r="170">
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>507.33</v>
+        <v>509.31</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3159-109-CM26</t>
+          <t>1079967-372-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>114.45</v>
+        <v>236.46</v>
       </c>
     </row>
     <row r="172">
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>156.07</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1079967-372-CM26</t>
+          <t>3159-109-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>234.11</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>141.51</v>
+        <v>142.92</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>156.07</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>208.1</v>
+        <v>210.18</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>256.47</v>
+        <v>257.77</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>130.38</v>
+        <v>130.66</v>
       </c>
     </row>
     <row r="179">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1507.5</v>
+        <v>1510.96</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1079967-420-CM26</t>
+          <t>1079967-419-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>130.38</v>
+        <v>185.33</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1079967-419-CM26</t>
+          <t>1079967-420-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>184.1</v>
+        <v>131.25</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3145-431-CM26</t>
+          <t>3145-430-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>834.4299999999999</v>
+        <v>472.51</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3145-430-CM26</t>
+          <t>3145-431-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>469.37</v>
+        <v>840.02</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>638.1</v>
+        <v>642.5599999999999</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1043.04</v>
+        <v>1039.75</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1434.18</v>
+        <v>1431.06</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>234.68</v>
+        <v>234.21</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1095.19</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>156.46</v>
+        <v>156.14</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>3899.13</v>
+        <v>3853.76</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>648.83</v>
+        <v>645.24</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>264.59</v>
+        <v>263.29</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1516.72</v>
+        <v>1526.88</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,129 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>488.93</v>
+        <v>492.2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1070620-7463-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>1063.64</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1407-496-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>618.5700000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/tarapaca.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M196"/>
+  <dimension ref="A1:M200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1250601-11-CM25</t>
+          <t>1407-15457-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>470.8</v>
+        <v>1441.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>794947-141-CM25</t>
+          <t>1350296-1754-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>173.15</v>
+        <v>3092.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3349-359-CM25</t>
+          <t>1079967-492-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2118.87</v>
+        <v>8772.790000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3349-363-CM25</t>
+          <t>1070620-17340-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>53.55</v>
+        <v>1011.31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3349-375-CM25</t>
+          <t>1250601-11-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro de Educación y Trabajo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1458.02</v>
+        <v>470.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3349-376-CM25</t>
+          <t>794947-141-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>233.42</v>
+        <v>173.15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2013-2038-CM25</t>
+          <t>3349-359-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>194.31</v>
+        <v>2118.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3145-622-CM25</t>
+          <t>3349-363-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>194.31</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1070620-28886-CM25</t>
+          <t>3349-375-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1025.27</v>
+        <v>1458.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1079967-637-CM25</t>
+          <t>3349-376-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>122.94</v>
+        <v>233.42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2013-2112-CM25</t>
+          <t>3145-622-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>189.14</v>
+        <v>194.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3349-380-CM25</t>
+          <t>2013-2038-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,22 +1200,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>713.35</v>
+        <v>194.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1407-15753-CM25</t>
+          <t>1070620-28886-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>285.34</v>
+        <v>1025.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1227-211-CM25</t>
+          <t>2013-2112-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>237.78</v>
+        <v>189.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1227-212-CM25</t>
+          <t>1079967-637-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>692.3</v>
+        <v>122.94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>838102-125-CM25</t>
+          <t>1227-211-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>959.79</v>
+        <v>237.78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1407-15759-CM25</t>
+          <t>1407-15753-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>590.87</v>
+        <v>285.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3145-646-CM25</t>
+          <t>3349-380-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>778.3099999999999</v>
+        <v>713.35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3208-239-CM25</t>
+          <t>1227-212-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>121.61</v>
+        <v>692.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1350296-2418-CM25</t>
+          <t>838102-125-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2574.31</v>
+        <v>959.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1346281-188-CM25</t>
+          <t>1407-15759-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1076.82</v>
+        <v>590.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3159-162-CM25</t>
+          <t>3145-646-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>109.01</v>
+        <v>778.3099999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5126-122-CM25</t>
+          <t>3208-239-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,22 +1871,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.979.650-0</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>382.89</v>
+        <v>121.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1079967-676-CM25</t>
+          <t>1350296-2418-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>65.76000000000001</v>
+        <v>2574.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1070620-29561-CM25</t>
+          <t>3159-162-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>984.1</v>
+        <v>109.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3145-649-CM25</t>
+          <t>1346281-188-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>234.91</v>
+        <v>1076.82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3352-293-CM25</t>
+          <t>1079967-676-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1187.7</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1347772-74-CM25</t>
+          <t>5126-122-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.979.650-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1030.23</v>
+        <v>382.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1250601-18-CM25</t>
+          <t>1070620-29561-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>440.79</v>
+        <v>984.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1407-15842-CM25</t>
+          <t>3145-649-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>587.85</v>
+        <v>234.91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3145-655-CM25</t>
+          <t>3352-293-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>288.54</v>
+        <v>1187.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3061-323-CM25</t>
+          <t>1347772-74-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>865.62</v>
+        <v>1030.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1079967-682-CM25</t>
+          <t>1250601-18-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Centro de Educación y Trabajo</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>881.78</v>
+        <v>440.79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2013-2113-CM25</t>
+          <t>1079967-682-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>193.41</v>
+        <v>881.78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1079967-704-CM25</t>
+          <t>3145-655-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>142.7</v>
+        <v>288.54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1407-15855-CM25</t>
+          <t>3061-323-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Comandancia Base Naval Iquique</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>428.77</v>
+        <v>865.62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3349-416-CM25</t>
+          <t>1407-15842-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>55.46</v>
+        <v>587.85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1070620-31700-CM25</t>
+          <t>2013-2113-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>996.6900000000001</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3145-681-CM25</t>
+          <t>1079967-704-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>759.9</v>
+        <v>142.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3145-682-CM25</t>
+          <t>3349-416-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>94.98999999999999</v>
+        <v>55.46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3208-246-CM25</t>
+          <t>1407-15855-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>142.22</v>
+        <v>428.77</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3208-247-CM25</t>
+          <t>1070620-31700-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>118.51</v>
+        <v>996.6900000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3100-100-CM25</t>
+          <t>3145-681-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1671.34</v>
+        <v>759.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1407-15894-CM25</t>
+          <t>3145-682-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>578.49</v>
+        <v>94.98999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1250601-25-CM25</t>
+          <t>3208-247-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>433.87</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>794947-162-CM25</t>
+          <t>3208-246-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>574.33</v>
+        <v>142.22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3239-2-CM26</t>
+          <t>3100-100-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.942.200-7</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ESTACION AERONAVAL IQUIQUE</t>
+          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>246.55</v>
+        <v>1671.34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1070620-248-CM26</t>
+          <t>1407-15894-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1035.52</v>
+        <v>578.49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>838102-3-CM26</t>
+          <t>1250601-25-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>Centro de Educación y Trabajo</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>979.1799999999999</v>
+        <v>433.87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1407-7-CM26</t>
+          <t>794947-162-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>608.25</v>
+        <v>574.33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3145-3-CM26</t>
+          <t>1070620-248-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>248.72</v>
+        <v>1035.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1079967-12-CM26</t>
+          <t>3239-2-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.942.200-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>ESTACION AERONAVAL IQUIQUE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>149.23</v>
+        <v>246.55</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1079967-13-CM26</t>
+          <t>838102-3-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>194.44</v>
+        <v>979.1799999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1227-6-CM26</t>
+          <t>1407-7-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>243.05</v>
+        <v>608.25</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3145-6-CM26</t>
+          <t>3145-3-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>787</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3061-22-CM26</t>
+          <t>1079967-12-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1215.48</v>
+        <v>149.23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1407-26-CM26</t>
+          <t>1079967-13-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>500.56</v>
+        <v>194.44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1070620-1018-CM26</t>
+          <t>1227-6-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,22 +4006,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1051.17</v>
+        <v>243.05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3159-9-CM26</t>
+          <t>3145-6-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>110.77</v>
+        <v>787</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3208-16-CM26</t>
+          <t>3061-22-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>Comandancia Base Naval Iquique</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>148.05</v>
+        <v>1215.48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3349-18-CM26</t>
+          <t>1070620-1018-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,22 +4189,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8398.25</v>
+        <v>1051.17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1407-35-CM26</t>
+          <t>1407-26-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>599.2</v>
+        <v>500.56</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1171177-1-CM26</t>
+          <t>3159-9-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>474.36</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3208-17-CM26</t>
+          <t>3208-16-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>146.33</v>
+        <v>148.05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1079967-23-CM26</t>
+          <t>3349-18-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>975.54</v>
+        <v>8398.25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3100-4-CM26</t>
+          <t>1407-35-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1089.86</v>
+        <v>599.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3100-5-CM26</t>
+          <t>1171177-1-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>Centro de Educación y Trabajo</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1512.09</v>
+        <v>474.36</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1350296-187-CM26</t>
+          <t>3208-17-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2711.36</v>
+        <v>146.33</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2948-66-CM26</t>
+          <t>1079967-23-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.102.051-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1545.25</v>
+        <v>975.54</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3100-7-CM26</t>
+          <t>3100-4-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>401.19</v>
+        <v>1089.86</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1079967-40-CM26</t>
+          <t>3100-5-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>122.24</v>
+        <v>1512.09</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3145-29-CM26</t>
+          <t>1350296-187-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,22 +4860,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>243.87</v>
+        <v>2711.36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3145-32-CM26</t>
+          <t>2948-66-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.102.051-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>Comandancia en Jefe de la IV Zona Naval</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>345.65</v>
+        <v>1545.25</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1070620-1664-CM26</t>
+          <t>3100-7-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,22 +4982,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1014.91</v>
+        <v>401.19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3349-31-CM26</t>
+          <t>1079967-40-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3386.02</v>
+        <v>122.24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3352-15-CM26</t>
+          <t>3145-29-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,22 +5104,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2074.79</v>
+        <v>243.87</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1426397-35-CM26</t>
+          <t>3145-32-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>143.33</v>
+        <v>345.65</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1407-69-CM26</t>
+          <t>1070620-1664-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>586.53</v>
+        <v>1014.91</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>935934-34-CM26</t>
+          <t>3349-31-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>129.53</v>
+        <v>3386.02</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1407-82-CM26</t>
+          <t>3352-15-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1377.45</v>
+        <v>2074.79</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3349-46-CM26</t>
+          <t>1426397-35-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1645.65</v>
+        <v>143.33</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2948-82-CM26</t>
+          <t>1407-69-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.102.051-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>226.53</v>
+        <v>586.53</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>838102-32-CM26</t>
+          <t>935934-34-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>Zona de Bienestar Iquique</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>968.5599999999999</v>
+        <v>129.53</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2013-238-CM26</t>
+          <t>1407-82-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,27 +5587,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>188.42</v>
+        <v>1377.45</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3447-522-CM26</t>
+          <t>2948-82-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.102.051-1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>Comandancia en Jefe de la IV Zona Naval</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1968.42</v>
+        <v>226.53</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>722640-31-CM26</t>
+          <t>3349-46-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.250.400-3</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLCHANE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>232.65</v>
+        <v>1645.65</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2591-140-CM26</t>
+          <t>838102-32-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,27 +5770,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>384.99</v>
+        <v>968.5599999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1070620-2377-CM26</t>
+          <t>2013-238-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>999.42</v>
+        <v>188.42</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1171177-12-CM26</t>
+          <t>3447-522-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>460.84</v>
+        <v>1968.42</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1077499-14-CM26</t>
+          <t>2591-140-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>338.95</v>
+        <v>384.99</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3145-76-CM26</t>
+          <t>722640-31-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>69.250.400-3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>I MUNICIPALIDAD DE COLCHANE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>771.5</v>
+        <v>232.65</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3145-79-CM26</t>
+          <t>1070620-2377-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,22 +6080,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>241.09</v>
+        <v>999.42</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1024-29-CM26</t>
+          <t>1171177-12-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Centro de Educación y Trabajo</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>145.84</v>
+        <v>460.84</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1407-123-CM26</t>
+          <t>1077499-14-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>593.21</v>
+        <v>338.95</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1079967-90-CM26</t>
+          <t>3145-79-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>144.91</v>
+        <v>241.09</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1079967-91-CM26</t>
+          <t>1024-29-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>193.22</v>
+        <v>145.84</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1407-163-CM26</t>
+          <t>3145-76-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>479.82</v>
+        <v>771.5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1070620-2944-CM26</t>
+          <t>1407-123-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1006.96</v>
+        <v>593.21</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>794947-26-CM26</t>
+          <t>1079967-91-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,22 +6507,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>215.78</v>
+        <v>193.22</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2591-211-CM26</t>
+          <t>1079967-90-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,22 +6568,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>234.95</v>
+        <v>144.91</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3061-75-CM26</t>
+          <t>1407-163-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1405.51</v>
+        <v>479.82</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1227-79-CM26</t>
+          <t>794947-26-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,22 +6690,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>240.26</v>
+        <v>215.78</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3100-15-CM26</t>
+          <t>2591-211-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,22 +6751,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1907.61</v>
+        <v>234.95</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1407-186-CM26</t>
+          <t>1070620-2944-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,27 +6807,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>718.3200000000001</v>
+        <v>1006.96</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1171177-15-CM26</t>
+          <t>3061-75-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>Comandancia Base Naval Iquique</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>568.67</v>
+        <v>1405.51</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3349-93-CM26</t>
+          <t>1227-79-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7871.88</v>
+        <v>240.26</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3208-72-CM26</t>
+          <t>3100-15-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>180.64</v>
+        <v>1907.61</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3208-73-CM26</t>
+          <t>1407-186-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>180.64</v>
+        <v>718.3200000000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3349-97-CM26</t>
+          <t>1171177-15-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Centro de Educación y Trabajo</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>181.64</v>
+        <v>568.67</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3159-52-CM26</t>
+          <t>3349-93-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,22 +7178,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>646.5700000000001</v>
+        <v>7871.88</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1079967-175-CM26</t>
+          <t>3208-73-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>236.04</v>
+        <v>180.64</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1350296-674-CM26</t>
+          <t>3208-72-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>4023.34</v>
+        <v>180.64</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2404-389-CM26</t>
+          <t>3349-97-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>486.21</v>
+        <v>181.64</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2591-272-CM26</t>
+          <t>3159-52-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>929.92</v>
+        <v>646.5700000000001</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>838102-47-CM26</t>
+          <t>1350296-674-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>958.1</v>
+        <v>4023.34</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1407-215-CM26</t>
+          <t>1079967-175-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>728.41</v>
+        <v>236.04</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2591-328-CM26</t>
+          <t>2404-389-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>434.52</v>
+        <v>486.21</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1070620-3938-CM26</t>
+          <t>2591-272-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1210.12</v>
+        <v>929.92</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1794-14-CM26</t>
+          <t>838102-47-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>313.89</v>
+        <v>958.1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3208-95-CM26</t>
+          <t>1407-215-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>171.42</v>
+        <v>728.41</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1079967-209-CM26</t>
+          <t>2591-328-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7844,27 +7844,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>142.65</v>
+        <v>434.52</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1227-117-CM26</t>
+          <t>1070620-3938-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7905,27 +7905,27 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>882.24</v>
+        <v>1210.12</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1227-116-CM26</t>
+          <t>3208-95-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>289</v>
+        <v>171.42</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3145-246-CM26</t>
+          <t>1794-14-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8027,27 +8027,27 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>289</v>
+        <v>313.89</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3145-248-CM26</t>
+          <t>1079967-209-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>929.54</v>
+        <v>142.65</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3349-126-CM26</t>
+          <t>3145-246-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,22 +8154,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1481.28</v>
+        <v>289</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3061-128-CM26</t>
+          <t>1227-116-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1938.4</v>
+        <v>289</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1171177-20-CM26</t>
+          <t>1227-117-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>591.17</v>
+        <v>882.24</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3159-62-CM26</t>
+          <t>3145-248-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>129.89</v>
+        <v>929.54</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1407-265-CM26</t>
+          <t>3349-126-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>785.42</v>
+        <v>1481.28</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3100-26-CM26</t>
+          <t>3061-128-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8459,22 +8459,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>Comandancia Base Naval Iquique</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2676.97</v>
+        <v>1938.4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1346281-73-CM26</t>
+          <t>1171177-20-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Centro de Educación y Trabajo</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1687.47</v>
+        <v>591.17</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>707412-42-CM26</t>
+          <t>3159-62-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,22 +8581,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2921.66</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1407-288-CM26</t>
+          <t>1407-265-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>627.72</v>
+        <v>785.42</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1426404-18-CM26</t>
+          <t>3100-26-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,22 +8703,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1723.26</v>
+        <v>2676.97</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3208-108-CM26</t>
+          <t>1346281-73-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>190.64</v>
+        <v>1687.47</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1079967-261-CM26</t>
+          <t>707412-42-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4800.23</v>
+        <v>2921.66</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1407-304-CM26</t>
+          <t>1407-288-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>775.35</v>
+        <v>627.72</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1350296-970-CM26</t>
+          <t>1426404-18-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3597.17</v>
+        <v>1723.26</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3235-306-CM26</t>
+          <t>3208-108-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.102.089-9</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>POLICLINICO MEDICO DENTAL IQUIQUE</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>270.65</v>
+        <v>190.64</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3349-179-CM26</t>
+          <t>1079967-261-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>19885.08</v>
+        <v>4800.23</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3352-94-CM26</t>
+          <t>1407-304-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>967.35</v>
+        <v>775.35</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3145-320-CM26</t>
+          <t>1350296-970-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9186,27 +9186,27 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>630.38</v>
+        <v>3597.17</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3145-322-CM26</t>
+          <t>3235-306-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.102.089-9</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>POLICLINICO MEDICO DENTAL IQUIQUE</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>315.19</v>
+        <v>270.65</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3145-324-CM26</t>
+          <t>3349-179-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9308,27 +9308,27 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1008.6</v>
+        <v>19885.08</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1347772-40-CM26</t>
+          <t>3352-94-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9369,27 +9369,27 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1296.82</v>
+        <v>967.35</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>838102-63-CM26</t>
+          <t>1347772-40-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,22 +9435,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>890.97</v>
+        <v>1296.82</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1171177-21-CM26</t>
+          <t>3145-324-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9496,22 +9496,22 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>510.49</v>
+        <v>1008.6</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3061-162-CM26</t>
+          <t>3145-322-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1395.97</v>
+        <v>315.19</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5651-48-CM26</t>
+          <t>3145-320-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>407.6</v>
+        <v>630.38</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1079967-300-CM26</t>
+          <t>1171177-21-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Centro de Educación y Trabajo</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>279.32</v>
+        <v>510.49</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1079967-301-CM26</t>
+          <t>838102-63-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1117.29</v>
+        <v>890.97</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3100-34-CM26</t>
+          <t>3061-162-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,22 +9801,22 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>Comandancia Base Naval Iquique</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1787.66</v>
+        <v>1395.97</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1426397-171-CM26</t>
+          <t>5651-48-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>545.24</v>
+        <v>407.6</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1407-343-CM26</t>
+          <t>1079967-300-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>708.2</v>
+        <v>279.32</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1227-158-CM26</t>
+          <t>1079967-301-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>6653.79</v>
+        <v>1117.29</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3208-132-CM26</t>
+          <t>3100-34-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>176.38</v>
+        <v>1787.66</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3349-210-CM26</t>
+          <t>1426397-171-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2990.14</v>
+        <v>545.24</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3145-385-CM26</t>
+          <t>1407-343-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10167,22 +10167,22 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>899.6799999999999</v>
+        <v>708.2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3145-384-CM26</t>
+          <t>3208-132-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,22 +10228,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>871.5599999999999</v>
+        <v>176.38</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5690-81-CM26</t>
+          <t>1227-158-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>139.42</v>
+        <v>6653.79</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1070620-6109-CM26</t>
+          <t>3349-210-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10350,22 +10350,22 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1173.18</v>
+        <v>2990.14</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1407-382-CM26</t>
+          <t>3145-384-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10411,22 +10411,22 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>558.66</v>
+        <v>871.5599999999999</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3145-411-CM26</t>
+          <t>3145-385-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>279.33</v>
+        <v>899.6799999999999</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2549-9-CM26</t>
+          <t>5690-81-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>253.63</v>
+        <v>139.42</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1079967-336-CM26</t>
+          <t>1070620-6109-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10589,27 +10589,27 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1138.11</v>
+        <v>1173.18</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1227-173-CM26</t>
+          <t>1407-382-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10650,27 +10650,27 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>279.37</v>
+        <v>558.66</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1407-386-CM26</t>
+          <t>3145-411-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10711,27 +10711,27 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>682.87</v>
+        <v>279.33</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1171177-27-CM26</t>
+          <t>2549-9-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>509.31</v>
+        <v>253.63</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1079967-372-CM26</t>
+          <t>1227-173-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10838,22 +10838,22 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>236.46</v>
+        <v>279.37</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1079967-371-CM26</t>
+          <t>1079967-336-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>157.64</v>
+        <v>1138.11</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3159-109-CM26</t>
+          <t>1407-386-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10960,22 +10960,22 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>115.6</v>
+        <v>682.87</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>935934-157-CM26</t>
+          <t>1171177-27-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>Centro de Educación y Trabajo</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>142.92</v>
+        <v>509.31</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3208-144-CM26</t>
+          <t>3159-109-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>157.64</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2013-1150-CM26</t>
+          <t>1079967-371-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11143,22 +11143,22 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>210.18</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1053139-94-CM26</t>
+          <t>1079967-372-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>257.77</v>
+        <v>236.46</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1079967-413-CM26</t>
+          <t>935934-157-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Zona de Bienestar Iquique</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>130.66</v>
+        <v>142.92</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3352-134-CM26</t>
+          <t>3208-144-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11326,22 +11326,22 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1510.96</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1079967-419-CM26</t>
+          <t>2013-1150-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>185.33</v>
+        <v>210.18</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1079967-420-CM26</t>
+          <t>1053139-94-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11448,22 +11448,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>131.25</v>
+        <v>257.77</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3145-430-CM26</t>
+          <t>1079967-413-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11509,22 +11509,22 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>472.51</v>
+        <v>130.66</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3145-431-CM26</t>
+          <t>3352-134-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>840.02</v>
+        <v>1510.96</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1407-413-CM26</t>
+          <t>1079967-420-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>642.5599999999999</v>
+        <v>131.25</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3061-191-CM26</t>
+          <t>1079967-419-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11692,22 +11692,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>SECCIÓN COMPRAS I ZONA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1039.75</v>
+        <v>185.33</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3100-44-CM26</t>
+          <t>3145-430-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1431.06</v>
+        <v>472.51</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>794947-94-CM26</t>
+          <t>3145-431-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11814,22 +11814,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>234.21</v>
+        <v>840.02</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1070620-6798-CM26</t>
+          <t>1407-413-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11875,22 +11875,22 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1093</v>
+        <v>642.5599999999999</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3208-155-CM26</t>
+          <t>3061-191-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11936,22 +11936,22 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>Comandancia Base Naval Iquique</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>156.14</v>
+        <v>1039.75</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1350296-1371-CM26</t>
+          <t>3100-44-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>3853.76</v>
+        <v>1431.06</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1407-443-CM26</t>
+          <t>794947-94-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12058,22 +12058,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>645.24</v>
+        <v>234.21</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3145-443-CM26</t>
+          <t>1070620-6798-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12159,13 +12159,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>263.29</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1057448-294-CM26</t>
+          <t>3208-155-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12220,13 +12220,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1526.88</v>
+        <v>156.14</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1171177-34-CM26</t>
+          <t>1350296-1371-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12241,22 +12241,22 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12281,13 +12281,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>492.2</v>
+        <v>3853.76</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1070620-7463-CM26</t>
+          <t>1407-443-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12297,27 +12297,27 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12327,12 +12327,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12342,13 +12342,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1063.64</v>
+        <v>645.24</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1407-496-CM26</t>
+          <t>3145-443-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12358,27 +12358,27 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12403,6 +12403,250 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
+        <v>263.29</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1057448-294-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.606.100-3</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>1526.88</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1171177-34-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>50.937.880-0</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Centro de Educación y Trabajo</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>492.2</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1070620-7463-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>1063.64</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1407-496-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
         <v>618.5700000000001</v>
       </c>
     </row>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/tarapaca.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M299"/>
+  <dimension ref="A1:M318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3145-510-CM25</t>
+          <t>3208-167-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>777.42</v>
+        <v>110.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3208-167-CM25</t>
+          <t>3145-510-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>110.34</v>
+        <v>777.42</v>
       </c>
     </row>
     <row r="4">
@@ -758,7 +758,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1407-15458-CM25</t>
+          <t>1227-129-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>629.6799999999999</v>
+        <v>258.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1227-129-CM25</t>
+          <t>1407-15458-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>258.04</v>
+        <v>629.6799999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1246,7 +1246,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1171177-48-CM25</t>
+          <t>1407-15482-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>358.2</v>
+        <v>503.12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3208-179-CM25</t>
+          <t>1171177-48-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>150.94</v>
+        <v>358.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1407-15482-CM25</t>
+          <t>3208-179-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>503.12</v>
+        <v>150.94</v>
       </c>
     </row>
     <row r="17">
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3349-258-CM25</t>
+          <t>1350296-1625-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4948.23</v>
+        <v>3103.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1350296-1625-CM25</t>
+          <t>3349-258-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3103.27</v>
+        <v>4948.23</v>
       </c>
     </row>
     <row r="20">
@@ -1978,7 +1978,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3145-538-CM25</t>
+          <t>3145-540-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>793.1900000000001</v>
+        <v>495.75</v>
       </c>
     </row>
     <row r="27">
@@ -2100,7 +2100,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3145-540-CM25</t>
+          <t>3145-538-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>495.75</v>
+        <v>793.1900000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2270-213-CM25</t>
+          <t>2013-1235-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>153.27</v>
+        <v>201.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2013-1235-CM25</t>
+          <t>2270-213-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>201.92</v>
+        <v>153.27</v>
       </c>
     </row>
     <row r="31">
@@ -2466,7 +2466,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1070620-15787-CM25</t>
+          <t>1171177-50-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1047.46</v>
+        <v>456.67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1171177-50-CM25</t>
+          <t>1070620-15787-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2547,17 +2547,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>456.67</v>
+        <v>1047.46</v>
       </c>
     </row>
     <row r="36">
@@ -3686,7 +3686,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1407-15608-CM25</t>
+          <t>1171177-57-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>599.3200000000001</v>
+        <v>474.46</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1171177-57-CM25</t>
+          <t>1407-15608-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>474.46</v>
+        <v>599.3200000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3869,7 +3869,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1407-15615-CM25</t>
+          <t>3061-286-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>491.17</v>
+        <v>1154.25</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1079967-508-CM25</t>
+          <t>1079967-501-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>122.79</v>
+        <v>1080.57</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1070620-16806-CM25</t>
+          <t>1079967-507-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1031.45</v>
+        <v>196.47</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1079967-501-CM25</t>
+          <t>1079967-508-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1080.57</v>
+        <v>122.79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3061-286-CM25</t>
+          <t>1407-15615-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1154.25</v>
+        <v>491.17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1079967-507-CM25</t>
+          <t>1070620-16806-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>196.47</v>
+        <v>1031.45</v>
       </c>
     </row>
     <row r="63">
@@ -4784,7 +4784,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1250601-6-CM25</t>
+          <t>1407-15665-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>466.73</v>
+        <v>589.55</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1407-15665-CM25</t>
+          <t>1250601-6-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>589.55</v>
+        <v>466.73</v>
       </c>
     </row>
     <row r="74">
@@ -5150,7 +5150,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3208-226-CM25</t>
+          <t>3208-225-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>97.83</v>
+        <v>98.31999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3208-225-CM25</t>
+          <t>3208-226-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>98.31999999999999</v>
+        <v>97.83</v>
       </c>
     </row>
     <row r="80">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6004,7 +6004,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3145-622-CM25</t>
+          <t>2013-2038-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6065,7 +6065,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2013-2038-CM25</t>
+          <t>3145-622-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6187,7 +6187,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1079967-637-CM25</t>
+          <t>2013-2112-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6207,17 +6207,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>122.94</v>
+        <v>189.14</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2013-2112-CM25</t>
+          <t>1079967-637-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6268,17 +6268,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>189.14</v>
+        <v>122.94</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1227-212-CM25</t>
+          <t>3349-380-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>692.3</v>
+        <v>713.35</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1227-211-CM25</t>
+          <t>1407-15753-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>237.78</v>
+        <v>285.34</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1407-15753-CM25</t>
+          <t>1227-211-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>285.34</v>
+        <v>237.78</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3349-380-CM25</t>
+          <t>1227-212-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>713.35</v>
+        <v>692.3</v>
       </c>
     </row>
     <row r="101">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6858,7 +6858,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3159-162-CM25</t>
+          <t>1346281-188-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6878,17 +6878,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>109.01</v>
+        <v>1076.82</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1346281-188-CM25</t>
+          <t>3159-162-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6939,17 +6939,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1076.82</v>
+        <v>109.01</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5126-122-CM25</t>
+          <t>1079967-676-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7000,17 +7000,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.979.650-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>382.89</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1079967-676-CM25</t>
+          <t>5126-122-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7061,17 +7061,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.979.650-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>65.76000000000001</v>
+        <v>382.89</v>
       </c>
     </row>
     <row r="110">
@@ -7163,7 +7163,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3352-293-CM25</t>
+          <t>3145-649-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1187.7</v>
+        <v>234.91</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3145-649-CM25</t>
+          <t>3352-293-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>234.91</v>
+        <v>1187.7</v>
       </c>
     </row>
     <row r="113">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7407,7 +7407,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3145-655-CM25</t>
+          <t>3061-323-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>288.54</v>
+        <v>865.62</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3061-323-CM25</t>
+          <t>3145-655-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>865.62</v>
+        <v>288.54</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1079967-682-CM25</t>
+          <t>1407-15842-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7549,17 +7549,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>881.78</v>
+        <v>587.85</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1407-15842-CM25</t>
+          <t>1079967-682-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7610,17 +7610,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>587.85</v>
+        <v>881.78</v>
       </c>
     </row>
     <row r="119">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7773,7 +7773,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1407-15855-CM25</t>
+          <t>3349-416-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>428.77</v>
+        <v>55.46</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3349-416-CM25</t>
+          <t>1407-15855-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>55.46</v>
+        <v>428.77</v>
       </c>
     </row>
     <row r="123">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>ESTACION AERONAVAL IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8566,7 +8566,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>838102-3-CM26</t>
+          <t>1417913-13-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8586,17 +8586,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>979.1799999999999</v>
+        <v>6185.69</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1407-7-CM26</t>
+          <t>838102-3-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>608.25</v>
+        <v>979.1799999999999</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3145-3-CM26</t>
+          <t>1407-7-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>248.72</v>
+        <v>608.25</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1079967-12-CM26</t>
+          <t>3145-3-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>149.23</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1227-6-CM26</t>
+          <t>1079967-12-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>243.05</v>
+        <v>149.23</v>
       </c>
     </row>
     <row r="139">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8932,7 +8932,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3145-6-CM26</t>
+          <t>1227-6-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>787</v>
+        <v>243.05</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3061-22-CM26</t>
+          <t>3145-6-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1215.48</v>
+        <v>787</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1407-26-CM26</t>
+          <t>3061-22-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>500.56</v>
+        <v>1215.48</v>
       </c>
     </row>
     <row r="143">
@@ -9176,7 +9176,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3159-9-CM26</t>
+          <t>1407-26-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>110.77</v>
+        <v>500.56</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3208-16-CM26</t>
+          <t>3159-9-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>148.05</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3349-18-CM26</t>
+          <t>3208-16-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>8398.25</v>
+        <v>148.05</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1407-35-CM26</t>
+          <t>3349-18-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9369,12 +9369,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>599.2</v>
+        <v>8398.25</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1171177-1-CM26</t>
+          <t>1407-35-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>474.36</v>
+        <v>599.2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3100-5-CM26</t>
+          <t>1171177-1-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1512.09</v>
+        <v>474.36</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3100-4-CM26</t>
+          <t>3208-17-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1089.86</v>
+        <v>146.33</v>
       </c>
     </row>
     <row r="151">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9664,7 +9664,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3208-17-CM26</t>
+          <t>3100-4-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>146.33</v>
+        <v>1089.86</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1350296-187-CM26</t>
+          <t>3100-5-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2711.36</v>
+        <v>1512.09</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2948-66-CM26</t>
+          <t>1350296-187-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.102.051-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1545.25</v>
+        <v>2711.36</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3100-7-CM26</t>
+          <t>2948-66-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>61.102.051-1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>401.19</v>
+        <v>1545.25</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1079967-40-CM26</t>
+          <t>3100-7-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>122.24</v>
+        <v>401.19</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3145-29-CM26</t>
+          <t>1079967-40-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9984,22 +9984,22 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>243.87</v>
+        <v>122.24</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3145-32-CM26</t>
+          <t>3145-29-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>345.65</v>
+        <v>243.87</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1070620-1664-CM26</t>
+          <t>3145-32-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10106,22 +10106,22 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1014.91</v>
+        <v>345.65</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3349-31-CM26</t>
+          <t>1070620-1664-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10167,22 +10167,22 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3386.02</v>
+        <v>1014.91</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3352-15-CM26</t>
+          <t>3349-31-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>2074.79</v>
+        <v>3386.02</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1426397-35-CM26</t>
+          <t>3352-15-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>143.33</v>
+        <v>2074.79</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1407-69-CM26</t>
+          <t>1426397-35-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>586.53</v>
+        <v>143.33</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>935934-34-CM26</t>
+          <t>1407-69-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>129.53</v>
+        <v>586.53</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1407-82-CM26</t>
+          <t>935934-34-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1377.45</v>
+        <v>129.53</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3349-46-CM26</t>
+          <t>1407-82-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1645.65</v>
+        <v>1377.45</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2948-82-CM26</t>
+          <t>3349-46-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.102.051-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>226.53</v>
+        <v>1645.65</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>838102-32-CM26</t>
+          <t>2948-82-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.102.051-1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>968.5599999999999</v>
+        <v>226.53</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2013-238-CM26</t>
+          <t>838102-32-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10711,27 +10711,27 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>188.42</v>
+        <v>968.5599999999999</v>
       </c>
     </row>
     <row r="170">
@@ -10823,7 +10823,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2591-140-CM26</t>
+          <t>2013-238-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>384.99</v>
+        <v>188.42</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>722640-31-CM26</t>
+          <t>2591-140-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10904,17 +10904,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.250.400-3</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLCHANE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>232.65</v>
+        <v>384.99</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1070620-2377-CM26</t>
+          <t>722640-31-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10960,22 +10960,22 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>69.250.400-3</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>I MUNICIPALIDAD DE COLCHANE</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>999.42</v>
+        <v>232.65</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1171177-12-CM26</t>
+          <t>1070620-2377-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11026,17 +11026,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>460.84</v>
+        <v>999.42</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1077499-14-CM26</t>
+          <t>1171177-12-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>338.95</v>
+        <v>460.84</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1024-29-CM26</t>
+          <t>1077499-14-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>145.84</v>
+        <v>338.95</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3145-79-CM26</t>
+          <t>3145-76-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>241.09</v>
+        <v>771.5</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3145-76-CM26</t>
+          <t>3145-79-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>771.5</v>
+        <v>241.09</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1407-123-CM26</t>
+          <t>1024-29-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>593.21</v>
+        <v>145.84</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1079967-90-CM26</t>
+          <t>1407-123-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>144.91</v>
+        <v>593.21</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1079967-91-CM26</t>
+          <t>1079967-90-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>193.22</v>
+        <v>144.91</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1407-163-CM26</t>
+          <t>1079967-91-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11519,12 +11519,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>479.82</v>
+        <v>193.22</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>794947-26-CM26</t>
+          <t>1407-163-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11570,22 +11570,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>215.78</v>
+        <v>479.82</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2591-211-CM26</t>
+          <t>794947-26-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>234.95</v>
+        <v>215.78</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1070620-2944-CM26</t>
+          <t>2591-211-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11702,12 +11702,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11717,12 +11717,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1006.96</v>
+        <v>234.95</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1227-79-CM26</t>
+          <t>1070620-2944-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11753,22 +11753,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>240.26</v>
+        <v>1006.96</v>
       </c>
     </row>
     <row r="187">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11860,7 +11860,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3100-15-CM26</t>
+          <t>1227-79-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1907.61</v>
+        <v>240.26</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1407-186-CM26</t>
+          <t>3100-15-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>718.3200000000001</v>
+        <v>1907.61</v>
       </c>
     </row>
     <row r="190">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3349-93-CM26</t>
+          <t>1407-186-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>7871.88</v>
+        <v>718.3200000000001</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3208-72-CM26</t>
+          <t>3349-93-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12159,13 +12159,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>180.64</v>
+        <v>7871.88</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3208-73-CM26</t>
+          <t>3208-72-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12226,7 +12226,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3159-52-CM26</t>
+          <t>3208-73-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12241,22 +12241,22 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>646.5700000000001</v>
+        <v>180.64</v>
       </c>
     </row>
     <row r="195">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12348,7 +12348,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1350296-674-CM26</t>
+          <t>3159-52-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12363,22 +12363,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>4023.34</v>
+        <v>646.5700000000001</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1079967-175-CM26</t>
+          <t>1350296-674-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>236.04</v>
+        <v>4023.34</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2404-389-CM26</t>
+          <t>1079967-175-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12485,22 +12485,22 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>486.21</v>
+        <v>236.04</v>
       </c>
     </row>
     <row r="199">
@@ -12592,7 +12592,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>838102-47-CM26</t>
+          <t>2404-389-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12607,22 +12607,22 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>958.1</v>
+        <v>486.21</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1407-215-CM26</t>
+          <t>838102-47-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>728.41</v>
+        <v>958.1</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2591-328-CM26</t>
+          <t>1407-215-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12729,22 +12729,22 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>434.52</v>
+        <v>728.41</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1070620-3938-CM26</t>
+          <t>2591-328-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12830,13 +12830,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1210.12</v>
+        <v>434.52</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3208-95-CM26</t>
+          <t>1070620-3938-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12851,22 +12851,22 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>171.42</v>
+        <v>1210.12</v>
       </c>
     </row>
     <row r="205">
@@ -12958,7 +12958,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1079967-209-CM26</t>
+          <t>3208-95-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12968,12 +12968,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>142.65</v>
+        <v>171.42</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3145-246-CM26</t>
+          <t>1079967-209-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13034,22 +13034,22 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>289</v>
+        <v>142.65</v>
       </c>
     </row>
     <row r="208">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13202,7 +13202,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3145-248-CM26</t>
+          <t>3145-246-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>929.54</v>
+        <v>289</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>3349-126-CM26</t>
+          <t>3145-248-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13278,22 +13278,22 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1481.28</v>
+        <v>929.54</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3061-128-CM26</t>
+          <t>3349-126-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13349,12 +13349,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1938.4</v>
+        <v>1481.28</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1171177-20-CM26</t>
+          <t>3061-128-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>591.17</v>
+        <v>1938.4</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>3159-62-CM26</t>
+          <t>1171177-20-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13461,22 +13461,22 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>129.89</v>
+        <v>591.17</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1407-265-CM26</t>
+          <t>3159-62-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13527,17 +13527,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>785.42</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3100-26-CM26</t>
+          <t>1407-265-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13583,22 +13583,22 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13623,13 +13623,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2676.97</v>
+        <v>785.42</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1346281-73-CM26</t>
+          <t>3100-26-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -13654,12 +13654,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1687.47</v>
+        <v>2676.97</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1407-288-CM26</t>
+          <t>1346281-73-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -13715,12 +13715,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>627.72</v>
+        <v>1687.47</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>707412-42-CM26</t>
+          <t>1407-288-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2921.66</v>
+        <v>627.72</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1426404-18-CM26</t>
+          <t>707412-42-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -13837,12 +13837,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1723.26</v>
+        <v>2921.66</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1079967-261-CM26</t>
+          <t>1426404-18-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>4800.23</v>
+        <v>1723.26</v>
       </c>
     </row>
     <row r="222">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13995,7 +13995,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1407-304-CM26</t>
+          <t>1079967-261-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14035,12 +14035,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14050,13 +14050,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>775.35</v>
+        <v>4800.23</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>3235-306-CM26</t>
+          <t>1407-304-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.102.089-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>POLICLINICO MEDICO DENTAL IQUIQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>270.65</v>
+        <v>775.35</v>
       </c>
     </row>
     <row r="225">
@@ -14178,7 +14178,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3349-179-CM26</t>
+          <t>3235-306-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -14203,12 +14203,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.102.089-9</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>19885.08</v>
+        <v>270.65</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>3352-94-CM26</t>
+          <t>3349-179-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14294,13 +14294,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>967.35</v>
+        <v>19885.08</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3145-320-CM26</t>
+          <t>3352-94-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14310,27 +14310,27 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14355,13 +14355,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>630.38</v>
+        <v>967.35</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>3145-322-CM26</t>
+          <t>1347772-40-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14381,17 +14381,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14401,12 +14401,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>315.19</v>
+        <v>1296.82</v>
       </c>
     </row>
     <row r="230">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14483,7 +14483,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1347772-40-CM26</t>
+          <t>3145-320-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14538,13 +14538,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1296.82</v>
+        <v>630.38</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>838102-63-CM26</t>
+          <t>3145-322-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -14569,12 +14569,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14599,13 +14599,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>890.97</v>
+        <v>315.19</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1171177-21-CM26</t>
+          <t>3159-78-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -14630,12 +14630,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -14660,13 +14660,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>510.49</v>
+        <v>947.21</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>3061-162-CM26</t>
+          <t>1171177-21-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -14691,12 +14691,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1395.97</v>
+        <v>510.49</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5651-48-CM26</t>
+          <t>838102-63-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -14752,12 +14752,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14782,13 +14782,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>407.6</v>
+        <v>890.97</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1079967-300-CM26</t>
+          <t>3061-162-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14843,13 +14843,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>279.32</v>
+        <v>1395.97</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1079967-301-CM26</t>
+          <t>1426397-171-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1117.29</v>
+        <v>545.24</v>
       </c>
     </row>
     <row r="238">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -14971,7 +14971,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1426397-171-CM26</t>
+          <t>1079967-301-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14996,12 +14996,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15026,13 +15026,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>545.24</v>
+        <v>1117.29</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1407-343-CM26</t>
+          <t>1079967-300-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -15057,12 +15057,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15072,12 +15072,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15087,13 +15087,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>708.2</v>
+        <v>279.32</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1227-158-CM26</t>
+          <t>5651-48-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -15118,12 +15118,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15148,13 +15148,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>6653.79</v>
+        <v>407.6</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3208-132-CM26</t>
+          <t>1407-343-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15169,22 +15169,22 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15209,13 +15209,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>176.38</v>
+        <v>708.2</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3349-210-CM26</t>
+          <t>1227-158-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15270,13 +15270,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2990.14</v>
+        <v>6653.79</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3145-384-CM26</t>
+          <t>3208-132-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15331,13 +15331,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>871.5599999999999</v>
+        <v>176.38</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3145-385-CM26</t>
+          <t>3349-210-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15352,22 +15352,22 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>899.6799999999999</v>
+        <v>2990.14</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5690-81-CM26</t>
+          <t>3145-384-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -15423,12 +15423,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15453,13 +15453,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>139.42</v>
+        <v>871.5599999999999</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1070620-6109-CM26</t>
+          <t>3145-385-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15514,13 +15514,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1173.18</v>
+        <v>899.6799999999999</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1407-382-CM26</t>
+          <t>5690-81-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15535,22 +15535,22 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15575,13 +15575,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>558.66</v>
+        <v>139.42</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>3145-411-CM26</t>
+          <t>1070620-6109-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15606,12 +15606,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15636,13 +15636,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>279.33</v>
+        <v>1173.18</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2549-9-CM26</t>
+          <t>1407-382-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15667,12 +15667,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15697,13 +15697,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>253.63</v>
+        <v>558.66</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1407-386-CM26</t>
+          <t>3145-411-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15713,27 +15713,27 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15743,12 +15743,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -15758,13 +15758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>682.87</v>
+        <v>279.33</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1227-173-CM26</t>
+          <t>2549-9-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15774,12 +15774,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>279.37</v>
+        <v>253.63</v>
       </c>
     </row>
     <row r="253">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15886,7 +15886,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1171177-27-CM26</t>
+          <t>1227-173-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -15911,12 +15911,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15926,12 +15926,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -15941,13 +15941,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>509.31</v>
+        <v>279.37</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3159-109-CM26</t>
+          <t>1407-386-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15962,22 +15962,22 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -15987,12 +15987,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -16002,13 +16002,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>115.6</v>
+        <v>682.87</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1079967-371-CM26</t>
+          <t>1171177-27-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>157.64</v>
+        <v>509.31</v>
       </c>
     </row>
     <row r="257">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16130,7 +16130,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>935934-157-CM26</t>
+          <t>1079967-371-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -16155,12 +16155,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16185,13 +16185,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>142.92</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3208-144-CM26</t>
+          <t>3159-109-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16246,13 +16246,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>157.64</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2013-1150-CM26</t>
+          <t>935934-157-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16272,17 +16272,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>210.18</v>
+        <v>142.92</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1053139-94-CM26</t>
+          <t>3208-144-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -16338,12 +16338,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>257.77</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1079967-413-CM26</t>
+          <t>2013-1150-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16389,22 +16389,22 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16429,13 +16429,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>130.66</v>
+        <v>210.18</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3352-134-CM26</t>
+          <t>1079967-413-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16475,12 +16475,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -16490,13 +16490,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1510.96</v>
+        <v>130.66</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>3145-430-CM26</t>
+          <t>3352-134-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16511,22 +16511,22 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16536,12 +16536,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -16551,13 +16551,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>472.51</v>
+        <v>1510.96</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3145-431-CM26</t>
+          <t>1079967-419-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16577,17 +16577,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>840.02</v>
+        <v>185.33</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1079967-419-CM26</t>
+          <t>1079967-420-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16673,13 +16673,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>185.33</v>
+        <v>131.25</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1079967-420-CM26</t>
+          <t>3145-430-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16699,17 +16699,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16734,13 +16734,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>131.25</v>
+        <v>472.51</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1407-413-CM26</t>
+          <t>3145-431-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16780,12 +16780,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -16795,13 +16795,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>642.5599999999999</v>
+        <v>840.02</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>3061-191-CM26</t>
+          <t>1407-413-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -16826,12 +16826,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16841,12 +16841,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -16856,13 +16856,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1039.75</v>
+        <v>642.5599999999999</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>3100-44-CM26</t>
+          <t>3061-191-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16877,22 +16877,22 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16917,13 +16917,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1431.06</v>
+        <v>1039.75</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>794947-94-CM26</t>
+          <t>3100-44-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16938,22 +16938,22 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -16978,13 +16978,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>234.21</v>
+        <v>1431.06</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1070620-6798-CM26</t>
+          <t>794947-94-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17009,12 +17009,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17039,13 +17039,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1093</v>
+        <v>234.21</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>3208-155-CM26</t>
+          <t>1070620-6798-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17100,13 +17100,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>156.14</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1350296-1371-CM26</t>
+          <t>3208-155-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17121,7 +17121,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17146,12 +17146,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17161,13 +17161,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>3853.76</v>
+        <v>156.14</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1407-443-CM26</t>
+          <t>1350296-1371-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17182,22 +17182,22 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17207,12 +17207,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -17222,13 +17222,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>645.24</v>
+        <v>3853.76</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3145-443-CM26</t>
+          <t>1407-443-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17243,22 +17243,22 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17268,12 +17268,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -17283,13 +17283,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>263.29</v>
+        <v>645.24</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1057448-294-CM26</t>
+          <t>3145-443-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -17314,12 +17314,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17329,12 +17329,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1526.88</v>
+        <v>263.29</v>
       </c>
     </row>
     <row r="278">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17411,7 +17411,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3208-176-CM26</t>
+          <t>1057448-294-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17421,27 +17421,27 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>160.57</v>
+        <v>1526.88</v>
       </c>
     </row>
     <row r="280">
@@ -17533,7 +17533,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3145-445-CM26</t>
+          <t>3208-176-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17548,22 +17548,22 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17588,13 +17588,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>498.04</v>
+        <v>160.57</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>3208-180-CM26</t>
+          <t>3145-445-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17609,22 +17609,22 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17649,13 +17649,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>162.92</v>
+        <v>498.04</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>4019-269-CM26</t>
+          <t>3208-180-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17680,12 +17680,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17695,12 +17695,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -17710,13 +17710,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>12152.52</v>
+        <v>162.92</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5126-79-CM26</t>
+          <t>4019-269-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -17741,12 +17741,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.979.650-0</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>ESTADO MAYOR CONJUNTO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17756,12 +17756,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17771,13 +17771,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>623.48</v>
+        <v>12152.52</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>4019-274-CM26</t>
+          <t>5126-79-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17802,12 +17802,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>61.979.650-0</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17817,12 +17817,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -17832,13 +17832,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>467.87</v>
+        <v>623.48</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1070620-7463-CM26</t>
+          <t>4019-274-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17853,22 +17853,22 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17878,12 +17878,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -17893,13 +17893,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1063.64</v>
+        <v>467.87</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>3145-469-CM26</t>
+          <t>1070620-7463-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -17924,12 +17924,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -17954,13 +17954,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>812.0599999999999</v>
+        <v>1063.64</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2591-543-CM26</t>
+          <t>3061-221-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17980,17 +17980,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18000,12 +18000,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K288" t="inlineStr"/>
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>3087.69</v>
+        <v>1294.23</v>
       </c>
     </row>
     <row r="289">
@@ -18082,7 +18082,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>3061-221-CM26</t>
+          <t>2591-543-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18102,17 +18102,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18122,12 +18122,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1294.23</v>
+        <v>3087.69</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1407-496-CM26</t>
+          <t>3145-469-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18158,22 +18158,22 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
@@ -18198,13 +18198,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>618.5700000000001</v>
+        <v>812.0599999999999</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1407-505-CM26</t>
+          <t>1407-496-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18244,12 +18244,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18259,13 +18259,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>503.76</v>
+        <v>618.5700000000001</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1079967-482-CM26</t>
+          <t>1407-505-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -18290,12 +18290,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18320,13 +18320,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>199.01</v>
+        <v>503.76</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1171177-37-CM26</t>
+          <t>1079967-482-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -18351,12 +18351,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>347.1</v>
+        <v>199.01</v>
       </c>
     </row>
     <row r="295">
@@ -18448,7 +18448,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>3239-17-CM26</t>
+          <t>1171177-37-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -18473,12 +18473,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.942.200-7</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18488,12 +18488,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>251.1</v>
+        <v>347.1</v>
       </c>
     </row>
     <row r="297">
@@ -18570,7 +18570,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1407-523-CM26</t>
+          <t>3239-17-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -18595,12 +18595,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.942.200-7</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18610,12 +18610,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -18625,13 +18625,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>749.1</v>
+        <v>251.1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3145-488-CM26</t>
+          <t>1407-523-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18646,22 +18646,22 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18671,12 +18671,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -18686,7 +18686,1166 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
+        <v>749.1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>3145-488-CM26</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>61.103.023-1</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="n">
         <v>247.17</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>1407-531-CM26</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="n">
+        <v>602.08</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>1350296-1614-CM26</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="n">
+        <v>2743.63</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>3349-313-CM26</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="n">
+        <v>1226.45</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2270-221-CM26</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="n">
+        <v>149.51</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>1070620-8377-CM26</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="n">
+        <v>1046.36</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>3061-251-CM26</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>61.962.400-9</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="n">
+        <v>1556.09</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>3145-515-CM26</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>61.103.023-1</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="n">
+        <v>614.91</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>3145-514-CM26</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>61.103.023-1</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="n">
+        <v>315.66</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>838102-98-CM26</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>73.923.800-5</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="n">
+        <v>791.22</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>3159-159-CM26</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>61.102.038-4</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="n">
+        <v>113.74</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1079967-534-CM26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>60.505.102-2</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>148.35</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>1171177-39-CM26</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>50.937.880-0</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="n">
+        <v>455.3</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>3145-526-CM26</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>61.103.023-1</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="n">
+        <v>874.67</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>5690-130-CM26</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="n">
+        <v>126.5</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>3100-58-CM26</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>61.102.002-3</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="n">
+        <v>717.08</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>1407-573-CM26</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="n">
+        <v>604.3099999999999</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>1347772-86-CM26</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="n">
+        <v>1093.47</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>1227-237-CM26</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>60.804.002-1</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M318" s="2" t="n">
+        <v>292.53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/tarapaca.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M465"/>
+  <dimension ref="A1:M482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1359,7 +1359,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3100-3-CM25</t>
+          <t>1070620-1022-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>15858.23</v>
+        <v>948.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>794947-2-CM25</t>
+          <t>3100-3-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>136.91</v>
+        <v>15858.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1070620-1022-CM25</t>
+          <t>794947-2-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>948.24</v>
+        <v>136.91</v>
       </c>
     </row>
     <row r="18">
@@ -2139,7 +2139,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3061-28-CM25</t>
+          <t>3208-17-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>858.25</v>
+        <v>135.51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3208-17-CM25</t>
+          <t>3061-28-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>135.51</v>
+        <v>858.25</v>
       </c>
     </row>
     <row r="29">
@@ -2789,7 +2789,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3239-2-CM25</t>
+          <t>794947-17-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.942.200-7</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>220.82</v>
+        <v>576.05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1171177-12-CM25</t>
+          <t>3239-2-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.942.200-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2894,17 +2894,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>425.25</v>
+        <v>220.82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>794947-17-CM25</t>
+          <t>1171177-12-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2959,17 +2959,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>576.05</v>
+        <v>425.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3352-35-CM25</t>
+          <t>1355-3-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.002.007-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3024,17 +3024,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3244.81</v>
+        <v>220.53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1355-3-CM25</t>
+          <t>3352-35-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.002.007-0</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>220.53</v>
+        <v>3244.81</v>
       </c>
     </row>
     <row r="42">
@@ -5909,7 +5909,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3447-1364-CM25</t>
+          <t>3145-320-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5949,17 +5949,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>138.96</v>
+        <v>290.92</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3145-320-CM25</t>
+          <t>3447-1364-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6014,17 +6014,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>290.92</v>
+        <v>138.96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1079967-180-CM25</t>
+          <t>1079967-178-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6104,7 +6104,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1070620-12020-CM25</t>
+          <t>1079967-179-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>951.5599999999999</v>
+        <v>181.25</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1079967-178-CM25</t>
+          <t>1079967-180-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6234,7 +6234,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1079967-179-CM25</t>
+          <t>1070620-12020-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>181.25</v>
+        <v>951.5599999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1350296-926-CM25</t>
+          <t>3145-329-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6319,17 +6319,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6339,17 +6339,17 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3048.48</v>
+        <v>1178.77</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3145-329-CM25</t>
+          <t>3145-333-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6423,13 +6423,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1178.77</v>
+        <v>362.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3145-333-CM25</t>
+          <t>1350296-926-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6469,17 +6469,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>362.7</v>
+        <v>3048.48</v>
       </c>
     </row>
     <row r="94">
@@ -6819,7 +6819,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1171177-32-CM25</t>
+          <t>3208-126-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6859,17 +6859,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>422.03</v>
+        <v>113.04</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3061-164-CM25</t>
+          <t>1171177-32-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6924,17 +6924,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>768.65</v>
+        <v>422.03</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>838102-65-CM25</t>
+          <t>3061-164-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>904.3</v>
+        <v>768.65</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3208-126-CM25</t>
+          <t>838102-65-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>113.04</v>
+        <v>904.3</v>
       </c>
     </row>
     <row r="103">
@@ -7274,7 +7274,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3159-67-CM25</t>
+          <t>935934-105-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7314,17 +7314,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>863.15</v>
+        <v>163.56</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>935934-105-CM25</t>
+          <t>3159-67-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7379,17 +7379,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>163.56</v>
+        <v>863.15</v>
       </c>
     </row>
     <row r="108">
@@ -7599,7 +7599,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3352-156-CM25</t>
+          <t>5651-63-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7658,13 +7658,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1570.84</v>
+        <v>263.98</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5651-63-CM25</t>
+          <t>3349-179-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7704,17 +7704,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>263.98</v>
+        <v>134.98</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3349-202-CM25</t>
+          <t>3349-183-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7769,17 +7769,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5108.54</v>
+        <v>2123.76</v>
       </c>
     </row>
     <row r="114">
@@ -7859,7 +7859,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3349-179-CM25</t>
+          <t>3349-202-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7899,17 +7899,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>134.98</v>
+        <v>5108.54</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3349-183-CM25</t>
+          <t>3352-156-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7964,17 +7964,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2123.76</v>
+        <v>1570.84</v>
       </c>
     </row>
     <row r="117">
@@ -8379,7 +8379,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3145-437-CM25</t>
+          <t>2013-771-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8399,17 +8399,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>763.46</v>
+        <v>169.66</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2013-771-CM25</t>
+          <t>3145-437-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8464,17 +8464,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>169.66</v>
+        <v>763.46</v>
       </c>
     </row>
     <row r="125">
@@ -8574,7 +8574,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1407-15390-CM25</t>
+          <t>1171177-40-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8614,17 +8614,17 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>380.31</v>
+        <v>412.87</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1171177-40-CM25</t>
+          <t>1407-15390-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -8679,17 +8679,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>412.87</v>
+        <v>380.31</v>
       </c>
     </row>
     <row r="128">
@@ -8834,7 +8834,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1350296-1315-CM25</t>
+          <t>838102-79-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8874,17 +8874,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8893,13 +8893,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3462.58</v>
+        <v>836.87</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>838102-79-CM25</t>
+          <t>1350296-1315-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8939,17 +8939,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>836.87</v>
+        <v>3462.58</v>
       </c>
     </row>
     <row r="132">
@@ -9094,7 +9094,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3208-154-CM25</t>
+          <t>1070620-14030-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9114,17 +9114,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>101.27</v>
+        <v>896.8</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1070620-14030-CM25</t>
+          <t>3208-154-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9179,17 +9179,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>896.8</v>
+        <v>101.27</v>
       </c>
     </row>
     <row r="136">
@@ -9354,7 +9354,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>707412-51-CM25</t>
+          <t>1407-15410-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9374,17 +9374,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9394,17 +9394,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>577.72</v>
+        <v>511.23</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1407-15410-CM25</t>
+          <t>600644-39-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9439,17 +9439,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.979.010-3</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9459,17 +9459,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9478,13 +9478,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>511.23</v>
+        <v>4272.98</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>600644-39-CM25</t>
+          <t>707412-51-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.979.010-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9524,17 +9524,17 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9543,7 +9543,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>4272.98</v>
+        <v>577.72</v>
       </c>
     </row>
     <row r="141">
@@ -10069,7 +10069,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3208-167-CM25</t>
+          <t>3145-510-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>110.34</v>
+        <v>777.42</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3145-510-CM25</t>
+          <t>3208-167-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>777.42</v>
+        <v>110.34</v>
       </c>
     </row>
     <row r="151">
@@ -10459,7 +10459,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1079967-363-CM25</t>
+          <t>3061-212-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10518,13 +10518,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>155.61</v>
+        <v>1400.53</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3061-212-CM25</t>
+          <t>1079967-363-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1400.53</v>
+        <v>155.61</v>
       </c>
     </row>
     <row r="157">
@@ -10914,7 +10914,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3208-179-CM25</t>
+          <t>1171177-48-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10954,17 +10954,17 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>150.94</v>
+        <v>358.2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1171177-48-CM25</t>
+          <t>3208-179-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11019,17 +11019,17 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>358.2</v>
+        <v>150.94</v>
       </c>
     </row>
     <row r="164">
@@ -11369,7 +11369,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3208-184-CM25</t>
+          <t>3208-186-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>121.37</v>
+        <v>98.93000000000001</v>
       </c>
     </row>
     <row r="170">
@@ -11499,7 +11499,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3208-186-CM25</t>
+          <t>3208-184-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>98.93000000000001</v>
+        <v>121.37</v>
       </c>
     </row>
     <row r="172">
@@ -11629,7 +11629,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3145-538-CM25</t>
+          <t>3145-539-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11688,13 +11688,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>793.1900000000001</v>
+        <v>148.72</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3145-539-CM25</t>
+          <t>3145-540-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>148.72</v>
+        <v>495.75</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3145-540-CM25</t>
+          <t>3145-538-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>495.75</v>
+        <v>793.1900000000001</v>
       </c>
     </row>
     <row r="176">
@@ -12149,7 +12149,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1079967-444-CM25</t>
+          <t>1171177-50-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12189,17 +12189,17 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>129.69</v>
+        <v>456.67</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1171177-50-CM25</t>
+          <t>1079967-444-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>456.67</v>
+        <v>129.69</v>
       </c>
     </row>
     <row r="183">
@@ -12929,7 +12929,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>600644-54-CM25</t>
+          <t>3208-205-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.979.010-3</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12988,13 +12988,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1669.69</v>
+        <v>98.22</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3208-205-CM25</t>
+          <t>600644-54-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>61.979.010-3</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DEL TAMARUGAL</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>98.22</v>
+        <v>1669.69</v>
       </c>
     </row>
     <row r="195">
@@ -13644,7 +13644,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3061-286-CM25</t>
+          <t>1070620-16806-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13664,17 +13664,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13703,13 +13703,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1154.25</v>
+        <v>1031.45</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1079967-501-CM25</t>
+          <t>3061-286-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1080.57</v>
+        <v>1154.25</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1079967-507-CM25</t>
+          <t>1079967-501-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13833,13 +13833,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>196.47</v>
+        <v>1080.57</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1079967-508-CM25</t>
+          <t>1079967-507-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>122.79</v>
+        <v>196.47</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1407-15615-CM25</t>
+          <t>1079967-508-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13963,13 +13963,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>491.17</v>
+        <v>122.79</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1070620-16806-CM25</t>
+          <t>1407-15615-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13989,17 +13989,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1031.45</v>
+        <v>491.17</v>
       </c>
     </row>
     <row r="210">
@@ -14359,7 +14359,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1070620-17340-CM25</t>
+          <t>3145-585-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14379,17 +14379,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14418,13 +14418,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1011.31</v>
+        <v>553.8099999999999</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3145-585-CM25</t>
+          <t>1070620-17340-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14444,17 +14444,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14483,7 +14483,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>553.8099999999999</v>
+        <v>1011.31</v>
       </c>
     </row>
     <row r="217">
@@ -15009,7 +15009,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3208-226-CM25</t>
+          <t>3208-225-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15068,13 +15068,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>97.83</v>
+        <v>98.31999999999999</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3208-225-CM25</t>
+          <t>3208-226-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>98.31999999999999</v>
+        <v>97.83</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1070620-17946-CM25</t>
+          <t>5690-162-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15159,17 +15159,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -15179,17 +15179,17 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -15198,13 +15198,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1022.67</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5690-162-CM25</t>
+          <t>1070620-17946-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15224,17 +15224,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15244,17 +15244,17 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -15263,7 +15263,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>115.99</v>
+        <v>1022.67</v>
       </c>
     </row>
     <row r="229">
@@ -15659,7 +15659,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3349-375-CM25</t>
+          <t>3349-359-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15718,7 +15718,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1458.02</v>
+        <v>2118.87</v>
       </c>
     </row>
     <row r="236">
@@ -15789,7 +15789,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3349-359-CM25</t>
+          <t>3349-375-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15848,7 +15848,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2118.87</v>
+        <v>1458.02</v>
       </c>
     </row>
     <row r="238">
@@ -15919,7 +15919,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3145-622-CM25</t>
+          <t>2013-2038-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15939,17 +15939,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15984,7 +15984,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2013-2038-CM25</t>
+          <t>3145-622-CM25</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -16004,17 +16004,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -16114,7 +16114,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2013-2112-CM25</t>
+          <t>1079967-637-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16134,17 +16134,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>189.14</v>
+        <v>122.94</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1079967-637-CM25</t>
+          <t>2013-2112-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16199,17 +16199,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16238,7 +16238,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>122.94</v>
+        <v>189.14</v>
       </c>
     </row>
     <row r="244">
@@ -16309,7 +16309,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1407-15753-CM25</t>
+          <t>1227-211-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16334,12 +16334,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>285.34</v>
+        <v>237.78</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1227-211-CM25</t>
+          <t>1227-212-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16414,17 +16414,17 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>237.78</v>
+        <v>692.3</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1227-212-CM25</t>
+          <t>1407-15753-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16464,12 +16464,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -16498,7 +16498,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>692.3</v>
+        <v>285.34</v>
       </c>
     </row>
     <row r="248">
@@ -17154,7 +17154,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3352-293-CM25</t>
+          <t>3145-649-CM25</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17179,12 +17179,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -17194,17 +17194,17 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -17213,13 +17213,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1187.7</v>
+        <v>234.91</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3145-649-CM25</t>
+          <t>3352-293-CM25</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17259,17 +17259,17 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>234.91</v>
+        <v>1187.7</v>
       </c>
     </row>
     <row r="260">
@@ -17414,7 +17414,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1407-15842-CM25</t>
+          <t>1079967-682-CM25</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17434,17 +17434,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17473,13 +17473,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>587.85</v>
+        <v>881.78</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3145-655-CM25</t>
+          <t>1407-15842-CM25</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17499,17 +17499,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17519,17 +17519,17 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -17538,7 +17538,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>288.54</v>
+        <v>587.85</v>
       </c>
     </row>
     <row r="264">
@@ -17609,7 +17609,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1079967-682-CM25</t>
+          <t>3145-655-CM25</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17634,12 +17634,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17649,17 +17649,17 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -17668,7 +17668,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>881.78</v>
+        <v>288.54</v>
       </c>
     </row>
     <row r="266">
@@ -18779,7 +18779,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3145-3-CM26</t>
+          <t>1407-7-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18819,17 +18819,17 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -18838,13 +18838,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>248.72</v>
+        <v>608.25</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1079967-12-CM26</t>
+          <t>3145-3-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18869,12 +18869,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>149.23</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1407-7-CM26</t>
+          <t>1079967-12-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18934,12 +18934,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18949,17 +18949,17 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -18968,7 +18968,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>608.25</v>
+        <v>149.23</v>
       </c>
     </row>
     <row r="286">
@@ -19689,7 +19689,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3208-17-CM26</t>
+          <t>1079967-23-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19714,12 +19714,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19748,13 +19748,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>146.33</v>
+        <v>975.54</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1079967-23-CM26</t>
+          <t>3100-4-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19779,12 +19779,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19794,17 +19794,17 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -19813,13 +19813,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>975.54</v>
+        <v>1089.86</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3100-4-CM26</t>
+          <t>3100-5-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19859,17 +19859,17 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -19878,13 +19878,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1089.86</v>
+        <v>1512.09</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3100-5-CM26</t>
+          <t>3208-17-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19909,7 +19909,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -19943,7 +19943,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1512.09</v>
+        <v>146.33</v>
       </c>
     </row>
     <row r="301">
@@ -21444,7 +21444,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>3145-76-CM26</t>
+          <t>1024-29-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -21469,12 +21469,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -21484,17 +21484,17 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -21503,13 +21503,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>771.5</v>
+        <v>145.84</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>3145-79-CM26</t>
+          <t>3145-76-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21568,13 +21568,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>241.09</v>
+        <v>771.5</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1024-29-CM26</t>
+          <t>3145-79-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21599,12 +21599,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21614,17 +21614,17 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -21633,7 +21633,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>145.84</v>
+        <v>241.09</v>
       </c>
     </row>
     <row r="327">
@@ -21899,7 +21899,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>794947-26-CM26</t>
+          <t>2591-211-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21924,12 +21924,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21939,17 +21939,17 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -21958,13 +21958,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>215.78</v>
+        <v>234.95</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2591-211-CM26</t>
+          <t>1070620-2944-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21989,12 +21989,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -22004,17 +22004,17 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -22023,13 +22023,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>234.95</v>
+        <v>1006.96</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1070620-2944-CM26</t>
+          <t>794947-26-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22054,12 +22054,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -22088,7 +22088,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1006.96</v>
+        <v>215.78</v>
       </c>
     </row>
     <row r="334">
@@ -22289,7 +22289,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1407-186-CM26</t>
+          <t>1171177-15-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22314,7 +22314,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -22348,13 +22348,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>718.3200000000001</v>
+        <v>568.67</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1171177-15-CM26</t>
+          <t>1407-186-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22379,7 +22379,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -22413,7 +22413,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>568.67</v>
+        <v>718.3200000000001</v>
       </c>
     </row>
     <row r="339">
@@ -22484,7 +22484,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>3208-72-CM26</t>
+          <t>3208-73-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22549,7 +22549,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3208-73-CM26</t>
+          <t>3208-72-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22744,7 +22744,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1079967-175-CM26</t>
+          <t>1350296-674-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22769,12 +22769,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22784,17 +22784,17 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>236.04</v>
+        <v>4023.34</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1350296-674-CM26</t>
+          <t>1079967-175-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22834,12 +22834,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22849,17 +22849,17 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -22868,7 +22868,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>4023.34</v>
+        <v>236.04</v>
       </c>
     </row>
     <row r="346">
@@ -23264,7 +23264,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1794-14-CM26</t>
+          <t>3208-95-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23289,12 +23289,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23304,17 +23304,17 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -23323,13 +23323,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>313.89</v>
+        <v>171.42</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>3208-95-CM26</t>
+          <t>1794-14-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23354,12 +23354,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -23369,17 +23369,17 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>171.42</v>
+        <v>313.89</v>
       </c>
     </row>
     <row r="354">
@@ -23459,7 +23459,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>3145-246-CM26</t>
+          <t>1227-117-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23479,17 +23479,17 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23499,17 +23499,17 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>289</v>
+        <v>882.24</v>
       </c>
     </row>
     <row r="356">
@@ -23589,7 +23589,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1227-117-CM26</t>
+          <t>3145-246-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23609,17 +23609,17 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23629,17 +23629,17 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -23648,7 +23648,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>882.24</v>
+        <v>289</v>
       </c>
     </row>
     <row r="358">
@@ -23719,7 +23719,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3349-126-CM26</t>
+          <t>1171177-20-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23744,12 +23744,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23759,17 +23759,17 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -23778,13 +23778,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1481.28</v>
+        <v>591.17</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>3061-128-CM26</t>
+          <t>3349-126-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23809,12 +23809,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23843,13 +23843,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1938.4</v>
+        <v>1481.28</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1171177-20-CM26</t>
+          <t>3061-128-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23874,12 +23874,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23889,17 +23889,17 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -23908,13 +23908,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>591.17</v>
+        <v>1938.4</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1407-265-CM26</t>
+          <t>3159-62-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23934,17 +23934,17 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23954,17 +23954,17 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -23973,13 +23973,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>785.42</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>3159-62-CM26</t>
+          <t>1407-265-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23999,17 +23999,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -24019,17 +24019,17 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -24038,7 +24038,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>129.89</v>
+        <v>785.42</v>
       </c>
     </row>
     <row r="364">
@@ -24369,7 +24369,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1407-304-CM26</t>
+          <t>3208-108-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24394,12 +24394,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -24409,17 +24409,17 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -24428,13 +24428,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>775.35</v>
+        <v>190.64</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>3208-108-CM26</t>
+          <t>1079967-261-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24459,12 +24459,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -24493,13 +24493,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>190.64</v>
+        <v>4800.23</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1079967-261-CM26</t>
+          <t>1407-304-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24524,12 +24524,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -24539,17 +24539,17 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>4800.23</v>
+        <v>775.35</v>
       </c>
     </row>
     <row r="372">
@@ -25149,7 +25149,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>838102-63-CM26</t>
+          <t>1171177-21-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -25174,12 +25174,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -25189,17 +25189,17 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -25208,13 +25208,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>890.97</v>
+        <v>510.49</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1171177-21-CM26</t>
+          <t>838102-63-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25239,12 +25239,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25254,17 +25254,17 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -25273,7 +25273,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>510.49</v>
+        <v>890.97</v>
       </c>
     </row>
     <row r="383">
@@ -25344,7 +25344,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>5651-48-CM26</t>
+          <t>1426397-171-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25369,12 +25369,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25403,13 +25403,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>407.6</v>
+        <v>545.24</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1079967-300-CM26</t>
+          <t>1079967-301-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25468,13 +25468,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>279.32</v>
+        <v>1117.29</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1079967-301-CM26</t>
+          <t>1079967-300-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25533,13 +25533,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>1117.29</v>
+        <v>279.32</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>3100-34-CM26</t>
+          <t>5651-48-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25564,12 +25564,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.102.002-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25598,13 +25598,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1787.66</v>
+        <v>407.6</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1426397-171-CM26</t>
+          <t>3100-34-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25629,12 +25629,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.102.002-3</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25663,7 +25663,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>545.24</v>
+        <v>1787.66</v>
       </c>
     </row>
     <row r="389">
@@ -25734,7 +25734,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>3208-132-CM26</t>
+          <t>1227-158-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25759,12 +25759,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25774,17 +25774,17 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -25793,13 +25793,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>176.38</v>
+        <v>6653.79</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1227-158-CM26</t>
+          <t>3208-132-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25824,12 +25824,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25839,17 +25839,17 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -25858,7 +25858,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>6653.79</v>
+        <v>176.38</v>
       </c>
     </row>
     <row r="392">
@@ -26189,7 +26189,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1407-382-CM26</t>
+          <t>3145-411-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26209,17 +26209,17 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -26248,13 +26248,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>558.66</v>
+        <v>279.33</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>3145-411-CM26</t>
+          <t>2549-9-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26274,17 +26274,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26313,13 +26313,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>279.33</v>
+        <v>253.63</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2549-9-CM26</t>
+          <t>1407-382-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26344,12 +26344,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26378,7 +26378,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>253.63</v>
+        <v>558.66</v>
       </c>
     </row>
     <row r="400">
@@ -26839,7 +26839,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>3208-144-CM26</t>
+          <t>2013-1150-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26864,12 +26864,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>61.102.083-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26898,13 +26898,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>157.64</v>
+        <v>210.18</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2013-1150-CM26</t>
+          <t>3208-144-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26929,12 +26929,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.102.083-K</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26963,7 +26963,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>210.18</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="409">
@@ -28464,7 +28464,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>5126-79-CM26</t>
+          <t>4019-274-CM26</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -28489,12 +28489,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>61.979.650-0</t>
+          <t>69.251.100-K</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>ESTADO MAYOR CONJUNTO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -28504,17 +28504,17 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -28523,13 +28523,13 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>623.48</v>
+        <v>467.87</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>4019-274-CM26</t>
+          <t>5126-79-CM26</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>69.251.100-K</t>
+          <t>61.979.650-0</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CAMINA</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -28569,17 +28569,17 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
@@ -28588,7 +28588,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>467.87</v>
+        <v>623.48</v>
       </c>
     </row>
     <row r="434">
@@ -28789,7 +28789,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2591-543-CM26</t>
+          <t>3145-469-CM26</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -28814,12 +28814,12 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>83.017.500-8</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -28829,17 +28829,17 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
@@ -28848,13 +28848,13 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>3087.69</v>
+        <v>812.0599999999999</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>3145-469-CM26</t>
+          <t>2591-543-CM26</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -28879,12 +28879,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>83.017.500-8</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -28894,17 +28894,17 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
@@ -28913,13 +28913,13 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>812.0599999999999</v>
+        <v>3087.69</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1407-496-CM26</t>
+          <t>1407-505-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28959,17 +28959,17 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -28978,13 +28978,13 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>618.5700000000001</v>
+        <v>503.76</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>1407-505-CM26</t>
+          <t>1407-496-CM26</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -29024,17 +29024,17 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -29043,7 +29043,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>503.76</v>
+        <v>618.5700000000001</v>
       </c>
     </row>
     <row r="441">
@@ -29829,7 +29829,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>3145-515-CM26</t>
+          <t>3061-251-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29849,17 +29849,17 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.962.400-9</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -29888,13 +29888,13 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>614.91</v>
+        <v>1556.09</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>3061-251-CM26</t>
+          <t>3145-515-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>61.962.400-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -29953,7 +29953,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>1556.09</v>
+        <v>614.91</v>
       </c>
     </row>
     <row r="455">
@@ -30024,7 +30024,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>838102-98-CM26</t>
+          <t>1171177-39-CM26</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -30049,12 +30049,12 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -30064,17 +30064,17 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -30083,13 +30083,13 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>791.22</v>
+        <v>455.3</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>3159-159-CM26</t>
+          <t>1079967-534-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -30109,17 +30109,17 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>60.505.102-2</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -30148,13 +30148,13 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>113.74</v>
+        <v>148.35</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>1079967-534-CM26</t>
+          <t>3159-159-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -30174,17 +30174,17 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>60.505.102-2</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -30213,13 +30213,13 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>148.35</v>
+        <v>113.74</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>1171177-39-CM26</t>
+          <t>838102-98-CM26</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -30244,12 +30244,12 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -30259,17 +30259,17 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
@@ -30278,7 +30278,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>455.3</v>
+        <v>791.22</v>
       </c>
     </row>
     <row r="460">
@@ -30564,7 +30564,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -30629,7 +30629,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -30669,6 +30669,1111 @@
       </c>
       <c r="M465" s="2" t="n">
         <v>292.53</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>3145-541-CM26</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>61.103.023-1</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M466" s="2" t="n">
+        <v>193.32</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>1070620-9032-CM26</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>62.000.530-4</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M467" s="2" t="n">
+        <v>1014.91</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>3352-182-CM26</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>61.101.024-9</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M468" s="2" t="n">
+        <v>1596.6</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>1407-599-CM26</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M469" s="2" t="n">
+        <v>477.77</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>794947-148-CM26</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>61.103.006-1</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M470" s="2" t="n">
+        <v>577.1900000000001</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>3100-62-CM26</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>61.102.002-3</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M471" s="2" t="n">
+        <v>823.78</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>3159-175-CM26</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>61.102.038-4</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M472" s="2" t="n">
+        <v>221.82</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2948-237-CM26</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>61.102.051-1</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M473" s="2" t="n">
+        <v>339.59</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>3208-236-CM26</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>61.102.083-K</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M474" s="2" t="n">
+        <v>131.45</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>3208-235-CM26</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>61.102.083-K</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M475" s="2" t="n">
+        <v>164.32</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>1407-624-CM26</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M476" s="2" t="n">
+        <v>651.0599999999999</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>5690-154-CM26</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M477" s="2" t="n">
+        <v>120.71</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>3061-285-CM26</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>61.962.400-9</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M478" s="2" t="n">
+        <v>1278.1</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>838102-112-CM26</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>73.923.800-5</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M479" s="2" t="n">
+        <v>889.11</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>3349-355-CM26</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M480" s="2" t="n">
+        <v>3331.31</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>1171177-48-CM26</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>50.937.880-0</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>ABASTIBLE S.A.</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>91.806.000-6</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M481" s="2" t="n">
+        <v>536.48</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>1350296-1995-CM26</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M482" s="2" t="n">
+        <v>4060.47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/tarapaca.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/tarapaca.xlsx
@@ -31799,7 +31799,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
